--- a/docs/Love Animals BCN - fichas de los animales.xlsx
+++ b/docs/Love Animals BCN - fichas de los animales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ALMA/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E6A15B-7E89-5B48-AA59-5549A2E5AA7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926DD269-0947-8B46-AD1B-A39E8A4F3086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="980" windowWidth="16680" windowHeight="9940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cómo se rellena" sheetId="1" r:id="rId1"/>
@@ -301,7 +301,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3187" uniqueCount="1364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3188" uniqueCount="1366">
   <si>
     <t>Fichas de los animales — Love Animals BCN</t>
   </si>
@@ -4324,15 +4324,9 @@
     <t>Silvy</t>
   </si>
   <si>
-    <t xml:space="preserve">Bibi </t>
-  </si>
-  <si>
     <t>Sakura</t>
   </si>
   <si>
-    <t>Seré tu bebita</t>
-  </si>
-  <si>
     <t>Cazadora de cartas y corazones</t>
   </si>
   <si>
@@ -4586,9 +4580,6 @@
   </si>
   <si>
     <t>60DF5C00-DE7F-43B7-94A0-3F75616ACDCB</t>
-  </si>
-  <si>
-    <t>E086413F-1E2F-46F4-923A-1184BFEE99E4</t>
   </si>
   <si>
     <t>ABB780A5-9BC5-4AF9-8D5C-F595635E5613</t>
@@ -4799,9 +4790,6 @@
   </si>
   <si>
     <t>IMG_6268.jpeg, IMG_6397.jpeg</t>
-  </si>
-  <si>
-    <t>, IMG_0471</t>
   </si>
   <si>
     <t xml:space="preserve">IMG_0871.jpeg,IMG_0862.jpeg, IMG_0872.jpeg, </t>
@@ -4935,26 +4923,6 @@
     <t>IMG_1410, IMG_1409, IMG_1408</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Cuerpo)"/>
-      </rPr>
-      <t>NO PONERLA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (https://www.instagram.com/p/DQXiAQMDexp) (https://www.instagram.com/p/DKpvDJltRRB)</t>
-    </r>
-  </si>
-  <si>
     <t>IMG_1394, IMG_1393, IMG_1395</t>
   </si>
   <si>
@@ -5038,6 +5006,27 @@
   </si>
   <si>
     <t>(https://www.instagram.com/p/DQrGwnajUer/?igsi=MWJtYWl4eGJxaXBxYw==) (https://www.instagram.com/p/CtrkSc_sdPL/?igsi=MWQ0MGJtM2Q3bDMyeA==)</t>
+  </si>
+  <si>
+    <t>Bibi &amp; Sepi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 años / 2 meses </t>
+  </si>
+  <si>
+    <t>Dos bebitas en uno</t>
+  </si>
+  <si>
+    <t>Bibi llegó embarazada a la protectora siendo ella todavia muy joven. Por suerte, encontramos una casa de acogida donde pudo dar a luz y tener a sus bebés. La mayoría fallecieron por culpa de un virus y solo una superviviente quedó: Sepi. Por ello, por todo lo que han sufrido y el vínculo que tienen, queremos que se vayan juntas. Ambas tienen muy buen carácter, son buenas, cariñosas, simpáticas y sociables. Dado que son súper jovencitas obviamente son activas y juguetonas. ¿Quieres ser feliz a su lado para siempre?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (https://www.instagram.com/p/DQXiAQMDexp) (https://www.instagram.com/p/DKpvDJltRRB)</t>
+  </si>
+  <si>
+    <t>IMG_0069, 9a6b3314-516d-4f5e-b80d-595d0e790c90,  IMG_0471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0744D68D-DFE1-4EBD-B82B-4C64A1F5F562, IMG_2135, IMG_2133, E086413F-1E2F-46F4-923A-1184BFEE99E4, </t>
   </si>
 </sst>
 </file>
@@ -6571,7 +6560,7 @@
         <v>130</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="R3" s="36" t="s">
         <v>762</v>
@@ -6626,7 +6615,7 @@
         <v>106</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="R4" s="36" t="s">
         <v>763</v>
@@ -6681,10 +6670,10 @@
         <v>110</v>
       </c>
       <c r="Q5" s="57" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="R5" s="37" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="S5" s="20"/>
     </row>
@@ -6736,7 +6725,7 @@
         <v>113</v>
       </c>
       <c r="Q6" s="19" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="R6" s="36" t="s">
         <v>764</v>
@@ -6791,7 +6780,7 @@
         <v>131</v>
       </c>
       <c r="Q7" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="R7" s="38" t="s">
         <v>792</v>
@@ -6846,7 +6835,7 @@
         <v>121</v>
       </c>
       <c r="Q8" s="19" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="R8" s="37" t="s">
         <v>752</v>
@@ -6901,7 +6890,7 @@
         <v>123</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="R9" s="36" t="s">
         <v>765</v>
@@ -6956,7 +6945,7 @@
         <v>132</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="R10" s="37" t="s">
         <v>753</v>
@@ -7011,7 +7000,7 @@
         <v>137</v>
       </c>
       <c r="Q11" s="19" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="R11" s="37" t="s">
         <v>789</v>
@@ -7066,7 +7055,7 @@
         <v>141</v>
       </c>
       <c r="Q12" s="19" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="R12" s="36" t="s">
         <v>766</v>
@@ -7121,7 +7110,7 @@
         <v>145</v>
       </c>
       <c r="Q13" s="19" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="R13" s="36" t="s">
         <v>767</v>
@@ -7176,7 +7165,7 @@
         <v>167</v>
       </c>
       <c r="Q14" s="19" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="R14" s="39" t="s">
         <v>754</v>
@@ -7231,7 +7220,7 @@
         <v>169</v>
       </c>
       <c r="Q15" s="19" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="R15" s="36" t="s">
         <v>768</v>
@@ -7286,7 +7275,7 @@
         <v>176</v>
       </c>
       <c r="Q16" s="19" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="R16" s="36" t="s">
         <v>769</v>
@@ -7341,7 +7330,7 @@
         <v>178</v>
       </c>
       <c r="Q17" s="19" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="R17" s="37" t="s">
         <v>755</v>
@@ -7396,7 +7385,7 @@
         <v>531</v>
       </c>
       <c r="Q18" s="19" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R18" s="36" t="s">
         <v>770</v>
@@ -7451,7 +7440,7 @@
         <v>182</v>
       </c>
       <c r="Q19" s="19" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="R19" s="39" t="s">
         <v>795</v>
@@ -7506,7 +7495,7 @@
         <v>185</v>
       </c>
       <c r="Q20" s="19" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="R20" s="39" t="s">
         <v>756</v>
@@ -7561,7 +7550,7 @@
         <v>188</v>
       </c>
       <c r="Q21" s="19" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="R21" s="36" t="s">
         <v>771</v>
@@ -7616,7 +7605,7 @@
         <v>199</v>
       </c>
       <c r="Q22" s="57" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="R22" s="37" t="s">
         <v>757</v>
@@ -7671,7 +7660,7 @@
         <v>203</v>
       </c>
       <c r="Q23" s="19" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="R23" s="37" t="s">
         <v>758</v>
@@ -7726,7 +7715,7 @@
         <v>205</v>
       </c>
       <c r="Q24" s="57" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="R24" s="37" t="s">
         <v>759</v>
@@ -7781,7 +7770,7 @@
         <v>206</v>
       </c>
       <c r="Q25" s="19" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="R25" s="37" t="s">
         <v>793</v>
@@ -7836,7 +7825,7 @@
         <v>208</v>
       </c>
       <c r="Q26" s="19" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="R26" s="37" t="s">
         <v>760</v>
@@ -7891,7 +7880,7 @@
         <v>210</v>
       </c>
       <c r="Q27" s="19" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="R27" s="37" t="s">
         <v>800</v>
@@ -7946,7 +7935,7 @@
         <v>212</v>
       </c>
       <c r="Q28" s="19" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="R28" s="39" t="s">
         <v>761</v>
@@ -8001,7 +7990,7 @@
         <v>192</v>
       </c>
       <c r="Q29" s="19" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="R29" s="39" t="s">
         <v>790</v>
@@ -8056,7 +8045,7 @@
         <v>196</v>
       </c>
       <c r="Q30" s="57" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="R30" s="38" t="s">
         <v>787</v>
@@ -8111,7 +8100,7 @@
         <v>221</v>
       </c>
       <c r="Q31" s="19" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="R31" s="39" t="s">
         <v>788</v>
@@ -8166,7 +8155,7 @@
         <v>458</v>
       </c>
       <c r="Q32" s="19" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="R32" s="39" t="s">
         <v>1123</v>
@@ -8221,7 +8210,7 @@
         <v>299</v>
       </c>
       <c r="Q33" s="19" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="R33" s="38" t="s">
         <v>791</v>
@@ -8276,7 +8265,7 @@
         <v>323</v>
       </c>
       <c r="Q34" s="19" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="R34" s="39" t="s">
         <v>794</v>
@@ -8331,7 +8320,7 @@
         <v>324</v>
       </c>
       <c r="Q35" s="19" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="R35" s="34" t="s">
         <v>859</v>
@@ -8386,7 +8375,7 @@
         <v>322</v>
       </c>
       <c r="Q36" s="19" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="R36" s="39" t="s">
         <v>796</v>
@@ -8441,7 +8430,7 @@
         <v>326</v>
       </c>
       <c r="Q37" s="19" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="R37" s="39" t="s">
         <v>797</v>
@@ -8496,7 +8485,7 @@
         <v>325</v>
       </c>
       <c r="Q38" s="19" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="R38" s="39" t="s">
         <v>798</v>
@@ -8551,7 +8540,7 @@
         <v>327</v>
       </c>
       <c r="Q39" s="19" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="R39" s="39" t="s">
         <v>799</v>
@@ -8606,7 +8595,7 @@
         <v>301</v>
       </c>
       <c r="Q40" s="19" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="R40" s="39" t="s">
         <v>775</v>
@@ -8661,7 +8650,7 @@
         <v>328</v>
       </c>
       <c r="Q41" s="57" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="R41" s="39" t="s">
         <v>772</v>
@@ -8716,7 +8705,7 @@
         <v>377</v>
       </c>
       <c r="Q42" s="19" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="R42" s="39" t="s">
         <v>777</v>
@@ -8771,7 +8760,7 @@
         <v>332</v>
       </c>
       <c r="Q43" s="19" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="R43" s="39" t="s">
         <v>850</v>
@@ -8826,7 +8815,7 @@
         <v>336</v>
       </c>
       <c r="Q44" s="19" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="R44" s="39" t="s">
         <v>785</v>
@@ -8881,7 +8870,7 @@
         <v>343</v>
       </c>
       <c r="Q45" s="19" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="R45" s="39" t="s">
         <v>783</v>
@@ -8936,7 +8925,7 @@
         <v>345</v>
       </c>
       <c r="Q46" s="19" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="R46" s="39" t="s">
         <v>778</v>
@@ -8991,7 +8980,7 @@
         <v>348</v>
       </c>
       <c r="Q47" s="69" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="R47" s="39" t="s">
         <v>784</v>
@@ -9046,7 +9035,7 @@
         <v>297</v>
       </c>
       <c r="Q48" s="19" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="R48" s="39" t="s">
         <v>779</v>
@@ -9101,7 +9090,7 @@
         <v>353</v>
       </c>
       <c r="Q49" s="19" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="R49" s="39" t="s">
         <v>773</v>
@@ -9156,7 +9145,7 @@
         <v>357</v>
       </c>
       <c r="Q50" s="19" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="R50" s="39" t="s">
         <v>1125</v>
@@ -9211,7 +9200,7 @@
         <v>367</v>
       </c>
       <c r="Q51" s="19" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="R51" s="39" t="s">
         <v>780</v>
@@ -9266,7 +9255,7 @@
         <v>374</v>
       </c>
       <c r="Q52" s="19" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="R52" s="39" t="s">
         <v>782</v>
@@ -9321,7 +9310,7 @@
         <v>360</v>
       </c>
       <c r="Q53" s="19" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="R53" s="39" t="s">
         <v>774</v>
@@ -9376,7 +9365,7 @@
         <v>362</v>
       </c>
       <c r="Q54" s="19" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="R54" s="19" t="s">
         <v>776</v>
@@ -9431,7 +9420,7 @@
         <v>365</v>
       </c>
       <c r="Q55" s="19" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="R55" s="39" t="s">
         <v>781</v>
@@ -9486,7 +9475,7 @@
         <v>379</v>
       </c>
       <c r="Q56" s="19" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="R56" s="39" t="s">
         <v>825</v>
@@ -9541,7 +9530,7 @@
         <v>391</v>
       </c>
       <c r="Q57" s="57" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="R57" s="39" t="s">
         <v>845</v>
@@ -9597,11 +9586,11 @@
       </c>
       <c r="Q58" s="19"/>
       <c r="R58" s="39" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="S58" s="20"/>
     </row>
-    <row r="59" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A59" s="16">
         <v>57</v>
       </c>
@@ -9649,7 +9638,7 @@
         <v>427</v>
       </c>
       <c r="Q59" s="57" t="s">
-        <v>1297</v>
+        <v>1364</v>
       </c>
       <c r="R59" s="39" t="s">
         <v>811</v>
@@ -9704,7 +9693,7 @@
         <v>395</v>
       </c>
       <c r="Q60" s="19" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="R60" s="39" t="s">
         <v>838</v>
@@ -9759,7 +9748,7 @@
         <v>398</v>
       </c>
       <c r="Q61" s="57" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="R61" s="39" t="s">
         <v>786</v>
@@ -9814,7 +9803,7 @@
         <v>402</v>
       </c>
       <c r="Q62" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="R62" s="39" t="s">
         <v>849</v>
@@ -9869,7 +9858,7 @@
         <v>405</v>
       </c>
       <c r="Q63" s="19" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="R63" s="39" t="s">
         <v>815</v>
@@ -9884,7 +9873,7 @@
         <v>441</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>423</v>
+        <v>349</v>
       </c>
       <c r="D64" s="17" t="s">
         <v>30</v>
@@ -9924,7 +9913,7 @@
         <v>461</v>
       </c>
       <c r="Q64" s="19" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="R64" s="39" t="s">
         <v>860</v>
@@ -9979,7 +9968,7 @@
         <v>411</v>
       </c>
       <c r="Q65" s="19" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="R65" s="39" t="s">
         <v>801</v>
@@ -10034,7 +10023,7 @@
         <v>421</v>
       </c>
       <c r="Q66" s="19" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="R66" s="39" t="s">
         <v>807</v>
@@ -10089,7 +10078,7 @@
         <v>408</v>
       </c>
       <c r="Q67" s="19" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="R67" s="39" t="s">
         <v>810</v>
@@ -10144,7 +10133,7 @@
         <v>418</v>
       </c>
       <c r="Q68" s="57" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="R68" s="39" t="s">
         <v>814</v>
@@ -10199,7 +10188,7 @@
         <v>432</v>
       </c>
       <c r="Q69" s="19" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="R69" s="39" t="s">
         <v>837</v>
@@ -10254,7 +10243,7 @@
         <v>415</v>
       </c>
       <c r="Q70" s="19" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="R70" s="38" t="s">
         <v>806</v>
@@ -10309,7 +10298,7 @@
         <v>426</v>
       </c>
       <c r="Q71" s="19" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="R71" s="39" t="s">
         <v>844</v>
@@ -10364,7 +10353,7 @@
         <v>390</v>
       </c>
       <c r="Q72" s="19" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="R72" s="39" t="s">
         <v>845</v>
@@ -10419,7 +10408,7 @@
         <v>503</v>
       </c>
       <c r="Q73" s="57" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="R73" s="39" t="s">
         <v>861</v>
@@ -10474,7 +10463,7 @@
         <v>465</v>
       </c>
       <c r="Q74" s="19" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="R74" s="39" t="s">
         <v>846</v>
@@ -10529,7 +10518,7 @@
         <v>484</v>
       </c>
       <c r="Q75" s="19" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="R75" s="39" t="s">
         <v>854</v>
@@ -10584,7 +10573,7 @@
         <v>487</v>
       </c>
       <c r="Q76" s="57" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="R76" s="38" t="s">
         <v>805</v>
@@ -10639,7 +10628,7 @@
         <v>496</v>
       </c>
       <c r="Q77" s="19" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="R77" s="39" t="s">
         <v>862</v>
@@ -10694,7 +10683,7 @@
         <v>498</v>
       </c>
       <c r="Q78" s="19" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="R78" s="39" t="s">
         <v>843</v>
@@ -10749,7 +10738,7 @@
         <v>435</v>
       </c>
       <c r="Q79" s="19" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="R79" s="39" t="s">
         <v>833</v>
@@ -10804,7 +10793,7 @@
         <v>490</v>
       </c>
       <c r="Q80" s="57" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="R80" s="39" t="s">
         <v>813</v>
@@ -10859,7 +10848,7 @@
         <v>446</v>
       </c>
       <c r="Q81" s="19" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="R81" s="39" t="s">
         <v>835</v>
@@ -10914,7 +10903,7 @@
         <v>438</v>
       </c>
       <c r="Q82" s="19" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="R82" s="39" t="s">
         <v>802</v>
@@ -10969,7 +10958,7 @@
         <v>469</v>
       </c>
       <c r="Q83" s="19" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="R83" s="39" t="s">
         <v>808</v>
@@ -11024,7 +11013,7 @@
         <v>460</v>
       </c>
       <c r="Q84" s="19" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="R84" s="39" t="s">
         <v>842</v>
@@ -11079,7 +11068,7 @@
         <v>497</v>
       </c>
       <c r="Q85" s="19" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="R85" s="39" t="s">
         <v>1120</v>
@@ -11134,10 +11123,10 @@
         <v>450</v>
       </c>
       <c r="Q86" s="19" t="s">
+        <v>1353</v>
+      </c>
+      <c r="R86" s="38" t="s">
         <v>1358</v>
-      </c>
-      <c r="R86" s="38" t="s">
-        <v>1363</v>
       </c>
       <c r="S86" s="20"/>
     </row>
@@ -11189,7 +11178,7 @@
         <v>476</v>
       </c>
       <c r="Q87" s="19" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="R87" s="39" t="s">
         <v>809</v>
@@ -11244,7 +11233,7 @@
         <v>472</v>
       </c>
       <c r="Q88" s="19" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="R88" s="39" t="s">
         <v>841</v>
@@ -11299,7 +11288,7 @@
         <v>479</v>
       </c>
       <c r="Q89" s="19" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="R89" s="39" t="s">
         <v>812</v>
@@ -11354,7 +11343,7 @@
         <v>502</v>
       </c>
       <c r="Q90" s="57" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="R90" s="39" t="s">
         <v>855</v>
@@ -11409,7 +11398,7 @@
         <v>506</v>
       </c>
       <c r="Q91" s="19" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="R91" s="39" t="s">
         <v>836</v>
@@ -11464,7 +11453,7 @@
         <v>566</v>
       </c>
       <c r="Q92" s="19" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="R92" s="39" t="s">
         <v>863</v>
@@ -11519,7 +11508,7 @@
         <v>509</v>
       </c>
       <c r="Q93" s="19" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="R93" s="39" t="s">
         <v>857</v>
@@ -11574,7 +11563,7 @@
         <v>513</v>
       </c>
       <c r="Q94" s="19" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="R94" s="39" t="s">
         <v>828</v>
@@ -11629,7 +11618,7 @@
         <v>526</v>
       </c>
       <c r="Q95" s="19" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="R95" s="39" t="s">
         <v>1122</v>
@@ -11684,7 +11673,7 @@
         <v>518</v>
       </c>
       <c r="Q96" s="19" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="R96" s="39" t="s">
         <v>816</v>
@@ -11739,7 +11728,7 @@
         <v>521</v>
       </c>
       <c r="Q97" s="58" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="R97" s="39" t="s">
         <v>834</v>
@@ -11794,10 +11783,10 @@
         <v>525</v>
       </c>
       <c r="Q98" s="19" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="R98" s="39" t="s">
-        <v>1335</v>
+        <v>1363</v>
       </c>
       <c r="S98" s="20"/>
     </row>
@@ -11902,7 +11891,7 @@
         <v>534</v>
       </c>
       <c r="Q100" s="19" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="R100" s="39" t="s">
         <v>864</v>
@@ -11957,7 +11946,7 @@
         <v>539</v>
       </c>
       <c r="Q101" s="19" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="R101" s="39" t="s">
         <v>865</v>
@@ -12012,7 +12001,7 @@
         <v>540</v>
       </c>
       <c r="Q102" s="19" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="R102" s="39" t="s">
         <v>858</v>
@@ -12067,7 +12056,7 @@
         <v>543</v>
       </c>
       <c r="Q103" s="19" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="R103" s="39" t="s">
         <v>1121</v>
@@ -12175,7 +12164,7 @@
         <v>546</v>
       </c>
       <c r="Q105" s="19" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="R105" s="39" t="s">
         <v>824</v>
@@ -12230,7 +12219,7 @@
         <v>530</v>
       </c>
       <c r="Q106" s="19" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="R106" s="39"/>
       <c r="S106" s="20"/>
@@ -12283,7 +12272,7 @@
         <v>554</v>
       </c>
       <c r="Q107" s="19" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="R107" s="39"/>
       <c r="S107" s="20"/>
@@ -12336,7 +12325,7 @@
         <v>555</v>
       </c>
       <c r="Q108" s="19" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="R108" s="39" t="s">
         <v>866</v>
@@ -12391,7 +12380,7 @@
         <v>550</v>
       </c>
       <c r="Q109" s="19" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="R109" s="39" t="s">
         <v>848</v>
@@ -12446,7 +12435,7 @@
         <v>558</v>
       </c>
       <c r="Q110" s="19" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="R110" s="39" t="s">
         <v>832</v>
@@ -12501,7 +12490,7 @@
         <v>561</v>
       </c>
       <c r="Q111" s="19" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="R111" s="39" t="s">
         <v>847</v>
@@ -12556,7 +12545,7 @@
         <v>563</v>
       </c>
       <c r="Q112" s="19" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="R112" s="39" t="s">
         <v>856</v>
@@ -12611,7 +12600,7 @@
         <v>589</v>
       </c>
       <c r="Q113" s="19" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="R113" s="39" t="s">
         <v>829</v>
@@ -12666,7 +12655,7 @@
         <v>596</v>
       </c>
       <c r="Q114" s="19" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="R114" s="39" t="s">
         <v>804</v>
@@ -12721,7 +12710,7 @@
         <v>597</v>
       </c>
       <c r="Q115" s="19" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="R115" s="39" t="s">
         <v>827</v>
@@ -12776,7 +12765,7 @@
         <v>602</v>
       </c>
       <c r="Q116" s="19" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="R116" s="39" t="s">
         <v>826</v>
@@ -12831,7 +12820,7 @@
         <v>603</v>
       </c>
       <c r="Q117" s="19" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="R117" s="39" t="s">
         <v>830</v>
@@ -12886,7 +12875,7 @@
         <v>604</v>
       </c>
       <c r="Q118" s="19" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="R118" s="39" t="s">
         <v>852</v>
@@ -12941,7 +12930,7 @@
         <v>611</v>
       </c>
       <c r="Q119" s="19" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="R119" s="39" t="s">
         <v>831</v>
@@ -12996,7 +12985,7 @@
         <v>615</v>
       </c>
       <c r="Q120" s="19" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="R120" s="38" t="s">
         <v>803</v>
@@ -13051,7 +13040,7 @@
         <v>616</v>
       </c>
       <c r="Q121" s="19" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="R121" s="39" t="s">
         <v>851</v>
@@ -13102,7 +13091,7 @@
         <v>868</v>
       </c>
       <c r="Q122" s="19" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="R122" s="50" t="s">
         <v>1096</v>
@@ -13154,7 +13143,7 @@
         <v>894</v>
       </c>
       <c r="Q123" s="19" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="R123" s="39" t="s">
         <v>1124</v>
@@ -13205,7 +13194,7 @@
         <v>897</v>
       </c>
       <c r="Q124" s="19" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="R124" s="39"/>
       <c r="S124" s="20"/>
@@ -13254,7 +13243,7 @@
         <v>888</v>
       </c>
       <c r="Q125" s="19" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="R125" s="50" t="s">
         <v>1098</v>
@@ -13305,7 +13294,7 @@
         <v>1137</v>
       </c>
       <c r="Q126" s="19" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="R126" s="39"/>
       <c r="S126" s="20"/>
@@ -13354,7 +13343,7 @@
         <v>878</v>
       </c>
       <c r="Q127" s="19" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="R127" s="50" t="s">
         <v>1097</v>
@@ -13405,7 +13394,7 @@
         <v>907</v>
       </c>
       <c r="Q128" s="19" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="R128" s="39" t="s">
         <v>1118</v>
@@ -13456,7 +13445,7 @@
         <v>891</v>
       </c>
       <c r="Q129" s="19" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="R129" s="50" t="s">
         <v>1105</v>
@@ -13507,7 +13496,7 @@
         <v>901</v>
       </c>
       <c r="Q130" s="19" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="R130" s="39"/>
       <c r="S130" s="20"/>
@@ -13556,7 +13545,7 @@
         <v>900</v>
       </c>
       <c r="Q131" s="19" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="R131" s="50" t="s">
         <v>1099</v>
@@ -13607,7 +13596,7 @@
         <v>902</v>
       </c>
       <c r="Q132" s="19" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="R132" s="39"/>
       <c r="S132" s="20"/>
@@ -13656,7 +13645,7 @@
         <v>903</v>
       </c>
       <c r="Q133" s="19" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="R133" s="50" t="s">
         <v>1095</v>
@@ -13707,7 +13696,7 @@
         <v>906</v>
       </c>
       <c r="Q134" s="19" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="R134" s="39"/>
       <c r="S134" s="20"/>
@@ -13756,7 +13745,7 @@
         <v>904</v>
       </c>
       <c r="Q135" s="19" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R135" s="39"/>
       <c r="S135" s="20"/>
@@ -13805,7 +13794,7 @@
         <v>905</v>
       </c>
       <c r="Q136" s="19" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="R136" s="39"/>
       <c r="S136" s="20"/>
@@ -13854,7 +13843,7 @@
         <v>929</v>
       </c>
       <c r="Q137" s="19" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="R137" s="50" t="s">
         <v>1094</v>
@@ -13954,7 +13943,7 @@
         <v>931</v>
       </c>
       <c r="Q139" s="19" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="R139" s="39"/>
       <c r="S139" s="20"/>
@@ -14003,7 +13992,7 @@
         <v>870</v>
       </c>
       <c r="Q140" s="19" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="R140" s="50" t="s">
         <v>1108</v>
@@ -14054,7 +14043,7 @@
         <v>874</v>
       </c>
       <c r="Q141" s="19" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="R141" s="39" t="s">
         <v>1107</v>
@@ -14105,7 +14094,7 @@
         <v>940</v>
       </c>
       <c r="Q142" s="19" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="R142" s="39"/>
       <c r="S142" s="20"/>
@@ -14154,7 +14143,7 @@
         <v>883</v>
       </c>
       <c r="Q143" s="19" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="R143" s="50" t="s">
         <v>1106</v>
@@ -14205,7 +14194,7 @@
         <v>956</v>
       </c>
       <c r="Q144" s="19" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="R144" s="39"/>
       <c r="S144" s="20"/>
@@ -14254,7 +14243,7 @@
         <v>941</v>
       </c>
       <c r="Q145" s="19" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="R145" s="39"/>
       <c r="S145" s="20"/>
@@ -14303,7 +14292,7 @@
         <v>928</v>
       </c>
       <c r="Q146" s="19" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="R146" s="50" t="s">
         <v>1109</v>
@@ -14354,7 +14343,7 @@
         <v>979</v>
       </c>
       <c r="Q147" s="19" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="R147" s="39"/>
       <c r="S147" s="20"/>
@@ -14403,7 +14392,7 @@
         <v>990</v>
       </c>
       <c r="Q148" s="19" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="R148" s="39"/>
       <c r="S148" s="20"/>
@@ -14499,7 +14488,7 @@
         <v>981</v>
       </c>
       <c r="Q150" s="19" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="R150" s="39"/>
       <c r="S150" s="20"/>
@@ -14548,7 +14537,7 @@
         <v>982</v>
       </c>
       <c r="Q151" s="19" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="R151" s="39"/>
       <c r="S151" s="20"/>
@@ -14597,7 +14586,7 @@
         <v>983</v>
       </c>
       <c r="Q152" s="19" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="R152" s="39"/>
       <c r="S152" s="20"/>
@@ -14646,7 +14635,7 @@
         <v>984</v>
       </c>
       <c r="Q153" s="19" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="R153" s="39"/>
       <c r="S153" s="20"/>
@@ -14695,7 +14684,7 @@
         <v>977</v>
       </c>
       <c r="Q154" s="19" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="R154" s="38" t="s">
         <v>1110</v>
@@ -14746,7 +14735,7 @@
         <v>985</v>
       </c>
       <c r="Q155" s="19" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="R155" s="39"/>
       <c r="S155" s="20"/>
@@ -14795,7 +14784,7 @@
         <v>986</v>
       </c>
       <c r="Q156" s="19" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="R156" s="39"/>
       <c r="S156" s="20"/>
@@ -14844,7 +14833,7 @@
         <v>988</v>
       </c>
       <c r="Q157" s="19" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="R157" s="39"/>
       <c r="S157" s="20"/>
@@ -14893,7 +14882,7 @@
         <v>989</v>
       </c>
       <c r="Q158" s="19" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="R158" s="39"/>
       <c r="S158" s="20"/>
@@ -15038,7 +15027,7 @@
         <v>728</v>
       </c>
       <c r="Q161" s="19" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="R161" s="50" t="s">
         <v>1090</v>
@@ -15089,7 +15078,7 @@
         <v>717</v>
       </c>
       <c r="Q162" s="19" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="R162" s="50" t="s">
         <v>1091</v>
@@ -15140,7 +15129,7 @@
         <v>714</v>
       </c>
       <c r="Q163" s="19" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="R163" s="50" t="s">
         <v>1088</v>
@@ -15191,7 +15180,7 @@
         <v>730</v>
       </c>
       <c r="Q164" s="19" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="R164" s="51" t="s">
         <v>1089</v>
@@ -15242,7 +15231,7 @@
         <v>953</v>
       </c>
       <c r="Q165" s="19" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="R165" s="39"/>
       <c r="S165" s="20"/>
@@ -15291,7 +15280,7 @@
         <v>713</v>
       </c>
       <c r="Q166" s="19" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="R166" s="50" t="s">
         <v>1085</v>
@@ -15342,7 +15331,7 @@
         <v>722</v>
       </c>
       <c r="Q167" s="19" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="R167" s="50" t="s">
         <v>1084</v>
@@ -15393,7 +15382,7 @@
         <v>992</v>
       </c>
       <c r="Q168" s="19" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="R168" s="50" t="s">
         <v>1083</v>
@@ -15444,7 +15433,7 @@
         <v>745</v>
       </c>
       <c r="Q169" s="19" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="R169" s="50" t="s">
         <v>1082</v>
@@ -15495,7 +15484,7 @@
         <v>744</v>
       </c>
       <c r="Q170" s="19" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="R170" s="50" t="s">
         <v>1081</v>
@@ -15545,7 +15534,7 @@
         <v>995</v>
       </c>
       <c r="Q171" s="19" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="R171" s="50" t="s">
         <v>1111</v>
@@ -15596,7 +15585,7 @@
         <v>1010</v>
       </c>
       <c r="Q172" s="19" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="R172" s="39"/>
       <c r="S172" s="20"/>
@@ -15645,7 +15634,7 @@
         <v>1012</v>
       </c>
       <c r="Q173" s="19" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="R173" s="39"/>
       <c r="S173" s="20"/>
@@ -15741,7 +15730,7 @@
         <v>1016</v>
       </c>
       <c r="Q175" s="19" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="R175" s="50" t="s">
         <v>1086</v>
@@ -15792,7 +15781,7 @@
         <v>748</v>
       </c>
       <c r="Q176" s="19" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="R176" s="39"/>
       <c r="S176" s="20"/>
@@ -15841,7 +15830,7 @@
         <v>1009</v>
       </c>
       <c r="Q177" s="19" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="R177" s="39"/>
       <c r="S177" s="20"/>
@@ -15888,7 +15877,7 @@
         <v>1008</v>
       </c>
       <c r="Q178" s="19" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="R178" s="39"/>
       <c r="S178" s="20"/>
@@ -15984,7 +15973,7 @@
         <v>738</v>
       </c>
       <c r="Q180" s="19" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="R180" s="39" t="s">
         <v>1087</v>
@@ -16035,7 +16024,7 @@
         <v>731</v>
       </c>
       <c r="Q181" s="19" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="R181" s="50" t="s">
         <v>1103</v>
@@ -16086,7 +16075,7 @@
         <v>729</v>
       </c>
       <c r="Q182" s="19" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="R182" s="50" t="s">
         <v>1092</v>
@@ -16137,7 +16126,7 @@
         <v>1020</v>
       </c>
       <c r="Q183" s="19" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="R183" s="50" t="s">
         <v>1114</v>
@@ -16188,7 +16177,7 @@
         <v>1026</v>
       </c>
       <c r="Q184" s="19" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="R184" s="32" t="s">
         <v>1112</v>
@@ -16239,7 +16228,7 @@
         <v>1030</v>
       </c>
       <c r="Q185" s="19" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="R185" s="39" t="s">
         <v>1113</v>
@@ -16290,7 +16279,7 @@
         <v>1023</v>
       </c>
       <c r="Q186" s="47" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="R186" s="39" t="s">
         <v>1113</v>
@@ -16341,7 +16330,7 @@
         <v>1022</v>
       </c>
       <c r="Q187" s="47" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="R187" s="39" t="s">
         <v>1113</v>
@@ -16392,7 +16381,7 @@
         <v>1013</v>
       </c>
       <c r="Q188" s="47" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="R188" s="39" t="s">
         <v>1113</v>
@@ -16443,7 +16432,7 @@
         <v>996</v>
       </c>
       <c r="Q189" s="19" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="R189" s="39"/>
       <c r="S189" s="20"/>
@@ -16492,7 +16481,7 @@
         <v>1000</v>
       </c>
       <c r="Q190" s="19" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="R190" s="50" t="s">
         <v>1115</v>
@@ -16541,7 +16530,7 @@
         <v>1001</v>
       </c>
       <c r="Q191" s="47" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="R191" s="50" t="s">
         <v>1115</v>
@@ -16590,7 +16579,7 @@
         <v>1002</v>
       </c>
       <c r="Q192" s="47" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="R192" s="50" t="s">
         <v>1115</v>
@@ -16602,7 +16591,7 @@
         <v>191</v>
       </c>
       <c r="B193" s="61" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C193" s="17" t="s">
         <v>92</v>
@@ -16641,7 +16630,7 @@
         <v>1045</v>
       </c>
       <c r="Q193" s="58" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="R193" s="50" t="s">
         <v>1116</v>
@@ -16692,7 +16681,7 @@
         <v>1048</v>
       </c>
       <c r="Q194" s="19" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="R194" s="50" t="s">
         <v>1116</v>
@@ -16743,7 +16732,7 @@
         <v>1054</v>
       </c>
       <c r="Q195" s="19" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="R195" s="50" t="s">
         <v>1116</v>
@@ -16793,7 +16782,7 @@
         <v>1057</v>
       </c>
       <c r="Q196" s="47" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="R196" s="38" t="s">
         <v>1117</v>
@@ -16844,7 +16833,7 @@
         <v>1014</v>
       </c>
       <c r="Q197" s="19" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="R197" s="39"/>
       <c r="S197" s="20"/>
@@ -16893,7 +16882,7 @@
         <v>1015</v>
       </c>
       <c r="Q198" s="19" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="R198" s="39"/>
       <c r="S198" s="20"/>
@@ -16942,7 +16931,7 @@
         <v>993</v>
       </c>
       <c r="Q199" s="19" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="R199" s="39"/>
       <c r="S199" s="20"/>
@@ -16991,7 +16980,7 @@
         <v>1070</v>
       </c>
       <c r="Q200" s="19" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="R200" s="38" t="s">
         <v>1117</v>
@@ -17042,7 +17031,7 @@
         <v>1071</v>
       </c>
       <c r="Q201" s="19" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="R201" s="39"/>
       <c r="S201" s="20"/>
@@ -17085,7 +17074,7 @@
         <v>997</v>
       </c>
       <c r="Q202" s="25" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="203" spans="1:19" x14ac:dyDescent="0.2">
@@ -17158,7 +17147,7 @@
         <v>1128</v>
       </c>
       <c r="Q204" s="42" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="205" spans="1:19" x14ac:dyDescent="0.2">
@@ -17199,7 +17188,7 @@
         <v>998</v>
       </c>
       <c r="Q205" s="42" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="206" spans="1:19" x14ac:dyDescent="0.2">
@@ -17313,7 +17302,7 @@
         <v>1133</v>
       </c>
       <c r="Q208" s="48" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="209" spans="2:20" x14ac:dyDescent="0.2">
@@ -17354,7 +17343,7 @@
         <v>991</v>
       </c>
       <c r="Q209" s="48" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="210" spans="2:20" x14ac:dyDescent="0.2">
@@ -17427,7 +17416,7 @@
         <v>1134</v>
       </c>
       <c r="Q211" s="48" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="212" spans="2:20" ht="30" x14ac:dyDescent="0.2">
@@ -17468,7 +17457,7 @@
         <v>1079</v>
       </c>
       <c r="Q212" s="48" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="R212" s="52" t="s">
         <v>1117</v>
@@ -17512,7 +17501,7 @@
         <v>1051</v>
       </c>
       <c r="Q213" s="48" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="R213" s="51" t="s">
         <v>1116</v>
@@ -17562,7 +17551,7 @@
         <v>1080</v>
       </c>
       <c r="Q214" s="47" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="R214" s="32" t="s">
         <v>821</v>
@@ -17612,7 +17601,7 @@
         <v>974</v>
       </c>
       <c r="Q215" s="47" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="R215" s="32" t="s">
         <v>822</v>
@@ -17662,7 +17651,7 @@
         <v>978</v>
       </c>
       <c r="Q216" s="47" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="R216" s="32" t="s">
         <v>840</v>
@@ -17712,7 +17701,7 @@
     </row>
     <row r="218" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B218" s="63" t="s">
-        <v>1139</v>
+        <v>1359</v>
       </c>
       <c r="C218" s="26" t="s">
         <v>92</v>
@@ -17727,7 +17716,7 @@
         <v>93</v>
       </c>
       <c r="H218" t="s">
-        <v>510</v>
+        <v>1360</v>
       </c>
       <c r="K218" s="47" t="s">
         <v>51</v>
@@ -17739,13 +17728,16 @@
         <v>51</v>
       </c>
       <c r="N218" s="47" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="O218" s="47" t="s">
-        <v>1141</v>
+        <v>1361</v>
+      </c>
+      <c r="P218" s="47" t="s">
+        <v>1362</v>
       </c>
       <c r="Q218" s="47" t="s">
-        <v>1227</v>
+        <v>1365</v>
       </c>
       <c r="R218" s="72" t="s">
         <v>1055</v>
@@ -17753,7 +17745,7 @@
     </row>
     <row r="219" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B219" s="49" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C219" s="26" t="s">
         <v>92</v>
@@ -17777,13 +17769,13 @@
         <v>51</v>
       </c>
       <c r="N219" s="47" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="O219" s="47" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="Q219" s="47" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="R219" s="72" t="s">
         <v>1055</v>
@@ -17791,10 +17783,10 @@
     </row>
     <row r="220" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B220" s="63" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="C220" s="26" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="D220" s="26" t="s">
         <v>85</v>
@@ -17824,21 +17816,21 @@
         <v>48</v>
       </c>
       <c r="N220" s="47" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="O220" s="47" t="s">
+        <v>1229</v>
+      </c>
+      <c r="P220" s="47" t="s">
+        <v>1230</v>
+      </c>
+      <c r="Q220" s="47" t="s">
         <v>1232</v>
-      </c>
-      <c r="P220" s="47" t="s">
-        <v>1233</v>
-      </c>
-      <c r="Q220" s="47" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="221" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B221" s="68" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="C221" s="26" t="s">
         <v>337</v>
@@ -17871,16 +17863,16 @@
         <v>55</v>
       </c>
       <c r="N221" s="47" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="O221" s="47" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="P221" s="47" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="Q221" s="47" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
     </row>
   </sheetData>
